--- a/docs/Evaluation Notes.xlsx
+++ b/docs/Evaluation Notes.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="109">
   <si>
     <t>Exact Match</t>
   </si>
@@ -483,6 +483,23 @@
 Custom questions often included more explicit company names, fiscal years, financial metrics, and source-document requirements. These details made them easier to answer than some benchmark questions. Additionally, successful ambiguity handling and broadly correct business descriptions did not necessarily demonstrate retrieval success.
 **Key finding:** Answer accuracy and retrieval quality are related but distinct. A RAG system can generate plausible answers from partially relevant evidence, while difficult benchmark questions expose weaknesses that simpler custom questions may not reveal.
 Future improvements should prioritize financial-table extraction, hybrid keyword and vector search, metadata filtering, source-evidence validation, and systematic retrieval evaluation using a consistent benchmark dataset.</t>
+  </si>
+  <si>
+    <t>As of 2022, the debt securities of American Express registered to trade on a national securities exchange include the following long-term debt issuances:
+Fixed Rate Senior Notes with a weighted-average coupon rate of 3.60%, totaling $10.2 billion
+Floating Rate Senior Notes (compounded SOFR plus weighted-average spread of 83 basis points), totaling $1.0 billion
+Fixed-to-Floating Rate Senior Notes (4.42% coupon during the fixed rate period and compounded SOFR plus 1.76% during the floating rate period), totaling $1.2 billion
+Fixed-to-Floating Rate Subordinated Notes (4.989% coupon during the fixed rate period and compounded SOFR plus 2.255% during the floating rate period), totaling $0.8 billion
+Fixed Rate Class A Certificates through the American Express Credit Account Master Trust, with a weighted-average coupon of 3.51%, totaling $7.3 billion
+The total amount of these debt securities is $20.5 billion.
+This information is from the 2022 Form 10-K filing of American Express, specifically under the section "Long-Term Debt and Asset Securitization Programs."</t>
+  </si>
+  <si>
+    <t>The knowledge base contains financial documents with data up to fiscal year 2018 for 3M. There is no available information in the documents regarding 3M's total revenue for fiscal year 2025. Therefore, I cannot provide the total revenue for 3M in fiscal year 2025 based on the financial documents in the knowledge base. If you have another request or a different fiscal year, please let me know.</t>
+  </si>
+  <si>
+    <t>American Express was able to retain card members in 2022. According to their 2022 10-K report, as of December 31, 2022, American Express had 76.7 million proprietary cards-in-force worldwide. The company focused on driving spending and increasing customer engagement through incentives such as the Membership Rewards program, cash-back features, interest rates on deposits, participation in loyalty programs, digital and mobile services, and various lifestyle and travel benefits. They also emphasized delivering exceptional customer care and developing partner relationships to provide benefits and services to card members. These efforts contributed to retaining and growing their card member base during the year.
+Source: American Express 2022 10-K, Card Products and Customer Engagement section.</t>
   </si>
 </sst>
 </file>
@@ -561,13 +578,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -583,6 +593,13 @@
     </xf>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -882,18 +899,18 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -1038,10 +1055,10 @@
       <c r="B20" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="8" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1071,12 +1088,12 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="92.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1100,38 +1117,38 @@
     <col min="5" max="5" width="67.33203125" style="7" customWidth="1"/>
     <col min="6" max="6" width="18.5546875" style="7" customWidth="1"/>
     <col min="7" max="7" width="44" style="7" customWidth="1"/>
-    <col min="8" max="8" width="9.21875" style="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="8.88671875" style="7"/>
     <col min="11" max="11" width="8.88671875" style="7" customWidth="1"/>
     <col min="12" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="10"/>
+      <c r="B1" s="16"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="9" t="s">
         <v>56</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="12" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1154,7 +1171,7 @@
       <c r="F3" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="H3" s="16"/>
+      <c r="H3" s="13"/>
     </row>
     <row r="4" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
@@ -1169,7 +1186,7 @@
       <c r="G4" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="13">
         <v>0.66666666666666663</v>
       </c>
     </row>
@@ -1180,6 +1197,9 @@
       <c r="B5" s="5" t="s">
         <v>39</v>
       </c>
+      <c r="C5" s="5" t="s">
+        <v>106</v>
+      </c>
       <c r="D5" s="5" t="s">
         <v>63</v>
       </c>
@@ -1189,7 +1209,7 @@
       <c r="G5" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="13">
         <v>0.33333333333333331</v>
       </c>
     </row>
@@ -1209,7 +1229,7 @@
       <c r="G6" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="13">
         <v>0.66666666666666663</v>
       </c>
     </row>
@@ -1232,7 +1252,7 @@
       <c r="G7" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="12" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1255,7 +1275,7 @@
       <c r="G8" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="12" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1266,6 +1286,9 @@
       <c r="B9" s="5" t="s">
         <v>21</v>
       </c>
+      <c r="C9" s="5" t="s">
+        <v>108</v>
+      </c>
       <c r="D9" s="5" t="s">
         <v>78</v>
       </c>
@@ -1278,7 +1301,7 @@
       <c r="G9" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="12" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1301,7 +1324,7 @@
       <c r="G10" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="H10" s="12" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1324,7 +1347,7 @@
       <c r="G11" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="H11" s="15" t="s">
+      <c r="H11" s="12" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1347,7 +1370,7 @@
       <c r="G12" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="H12" s="15" t="s">
+      <c r="H12" s="12" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1367,7 +1390,7 @@
       <c r="G13" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="H13" s="15" t="s">
+      <c r="H13" s="12" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1375,8 +1398,11 @@
       <c r="A14" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>98</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>99</v>
@@ -1390,7 +1416,7 @@
       <c r="G14" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="H14" s="12" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1413,12 +1439,12 @@
       <c r="G15" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="H15" s="15" t="s">
+      <c r="H15" s="12" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C16" s="14"/>
+      <c r="C16" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1435,7 +1461,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="15" t="s">
         <v>105</v>
       </c>
       <c r="B2" s="17"/>
